--- a/informes/informe_seguimiento_fernando_industriales.xlsx
+++ b/informes/informe_seguimiento_fernando_industriales.xlsx
@@ -243,6 +243,9 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -259,14 +262,11 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2686,7 +2686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2702,243 +2702,461 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
+    <row r="3" ht="20" customHeight="1">
       <c r="A3" s="22" t="inlineStr">
         <is>
+          <t>Proactividad comercial</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
           <t>Métrica</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Abr 2026</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>Objetivo</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="24" t="inlineStr">
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>ICC Proactividad</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>Digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>ICC Digital</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Calidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>ICC Calidad</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>Recursos generales</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>ICC Recursos</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>Carrocería</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>ICC Carrocería</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>ICC Personas</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="C25" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>Rankings de marca</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t>ICC posición global</t>
         </is>
       </c>
-      <c r="B4" s="25" t="n">
+      <c r="B29" s="26" t="n">
         <v>26</v>
       </c>
-      <c r="C4" s="26" t="inlineStr">
+      <c r="C29" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D4" s="27" t="inlineStr">
+      <c r="D29" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="28" t="inlineStr">
-        <is>
-          <t>ICC Proactividad</t>
-        </is>
-      </c>
-      <c r="B5" s="29" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="C5" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D5" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
-        <is>
-          <t>ICC Digital</t>
-        </is>
-      </c>
-      <c r="B6" s="25" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="C6" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D6" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="28" t="inlineStr">
-        <is>
-          <t>ICC Calidad</t>
-        </is>
-      </c>
-      <c r="B7" s="29" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="C7" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D7" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
-        <is>
-          <t>ICC Recursos</t>
-        </is>
-      </c>
-      <c r="B8" s="25" t="n">
-        <v>5.42</v>
-      </c>
-      <c r="C8" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="28" t="inlineStr">
-        <is>
-          <t>ICC Carrocería</t>
-        </is>
-      </c>
-      <c r="B9" s="29" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="C9" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D9" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
-        <is>
-          <t>ICC Personas</t>
-        </is>
-      </c>
-      <c r="B10" s="25" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="C10" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="28" t="inlineStr">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>ONE KVPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t>Score ONE</t>
         </is>
       </c>
-      <c r="B11" s="29" t="n">
+      <c r="B33" s="26" t="n">
         <v>6.8</v>
       </c>
-      <c r="C11" s="31" t="n">
+      <c r="C33" s="29" t="n">
         <v>6.1</v>
       </c>
-      <c r="D11" s="27" t="inlineStr">
+      <c r="D33" s="28" t="inlineStr">
         <is>
           <t>7,3</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="30" t="inlineStr">
         <is>
           <t>Service CAM (%)</t>
         </is>
       </c>
-      <c r="B12" s="25" t="n">
+      <c r="B34" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="C12" s="31" t="n">
+      <c r="C34" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="D12" s="27" t="inlineStr">
+      <c r="D34" s="28" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="28" t="inlineStr">
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
         <is>
           <t>Diferidos (%)</t>
         </is>
       </c>
-      <c r="B13" s="29" t="n">
+      <c r="B35" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C35" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="27" t="inlineStr">
+      <c r="D35" s="28" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="30" t="inlineStr">
         <is>
           <t>Multimedia</t>
         </is>
       </c>
-      <c r="B14" s="25" t="n">
+      <c r="B36" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="C14" s="32" t="n">
+      <c r="C36" s="32" t="n">
         <v>6.6</v>
       </c>
-      <c r="D14" s="27" t="inlineStr">
+      <c r="D36" s="28" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="9">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A11:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2967,22 +3185,22 @@
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Métrica</t>
         </is>
       </c>
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Referencia</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="23" t="inlineStr">
         <is>
           <t>Positivo si...</t>
         </is>
       </c>
-      <c r="D3" s="22" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t>Mejorar si...</t>
         </is>

--- a/informes/informe_seguimiento_fernando_industriales.xlsx
+++ b/informes/informe_seguimiento_fernando_industriales.xlsx
@@ -3124,7 +3124,7 @@
       </c>
       <c r="D35" s="28" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>15%</t>
         </is>
       </c>
     </row>

--- a/informes/informe_seguimiento_fernando_industriales.xlsx
+++ b/informes/informe_seguimiento_fernando_industriales.xlsx
@@ -2686,7 +2686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3048,7 +3048,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="22" t="inlineStr">
         <is>
-          <t>ONE KVPS</t>
+          <t>Cuadro CX</t>
         </is>
       </c>
     </row>
@@ -3077,81 +3077,131 @@
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="25" t="inlineStr">
         <is>
+          <t>CX total (/8)</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="C33" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D33" s="28" t="inlineStr">
+        <is>
+          <t>≥7</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>ONE KVPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Abr 2026</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
           <t>Score ONE</t>
         </is>
       </c>
-      <c r="B33" s="26" t="n">
+      <c r="B37" s="26" t="n">
         <v>6.8</v>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C37" s="29" t="n">
         <v>6.1</v>
       </c>
-      <c r="D33" s="28" t="inlineStr">
+      <c r="D37" s="28" t="inlineStr">
         <is>
           <t>7,3</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="30" t="inlineStr">
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="30" t="inlineStr">
         <is>
           <t>Service CAM (%)</t>
         </is>
       </c>
-      <c r="B34" s="31" t="n">
+      <c r="B38" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C38" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="D34" s="28" t="inlineStr">
+      <c r="D38" s="28" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="25" t="inlineStr">
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="25" t="inlineStr">
         <is>
           <t>Diferidos (%)</t>
         </is>
       </c>
-      <c r="B35" s="26" t="n">
+      <c r="B39" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="C35" s="26" t="n">
+      <c r="C39" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="D35" s="28" t="inlineStr">
+      <c r="D39" s="28" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="30" t="inlineStr">
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="30" t="inlineStr">
         <is>
           <t>Multimedia</t>
         </is>
       </c>
-      <c r="B36" s="31" t="n">
+      <c r="B40" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="C36" s="32" t="n">
+      <c r="C40" s="32" t="n">
         <v>6.6</v>
       </c>
-      <c r="D36" s="28" t="inlineStr">
+      <c r="D40" s="28" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A35:D35"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A7:D7"/>

--- a/informes/informe_seguimiento_fernando_industriales.xlsx
+++ b/informes/informe_seguimiento_fernando_industriales.xlsx
@@ -11,7 +11,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mar 20261" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abr 2026" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolución" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Objetivos" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -99,7 +98,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -141,16 +140,6 @@
         <fgColor rgb="00FADBD8"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EAF7EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDECEA"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -178,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -271,18 +260,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3210,144 +3187,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>Objetivos y umbrales de referencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
-        <is>
-          <t>Métrica</t>
-        </is>
-      </c>
-      <c r="B3" s="23" t="inlineStr">
-        <is>
-          <t>Referencia</t>
-        </is>
-      </c>
-      <c r="C3" s="23" t="inlineStr">
-        <is>
-          <t>Positivo si...</t>
-        </is>
-      </c>
-      <c r="D3" s="23" t="inlineStr">
-        <is>
-          <t>Mejorar si...</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="33" t="inlineStr">
-        <is>
-          <t>ONE Score SEM</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>Por encima de la media (7,3)</t>
-        </is>
-      </c>
-      <c r="C4" s="34" t="inlineStr">
-        <is>
-          <t>&gt;7,3</t>
-        </is>
-      </c>
-      <c r="D4" s="35" t="inlineStr">
-        <is>
-          <t>≤7,3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="36" t="inlineStr">
-        <is>
-          <t>ONE Service CAM</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>≥8%</t>
-        </is>
-      </c>
-      <c r="C5" s="34" t="inlineStr">
-        <is>
-          <t>≥8%</t>
-        </is>
-      </c>
-      <c r="D5" s="35" t="inlineStr">
-        <is>
-          <t>5-8% regular / &lt;5% mejorar</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="33" t="inlineStr">
-        <is>
-          <t>ONE Diferidos</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>≥8%</t>
-        </is>
-      </c>
-      <c r="C6" s="34" t="inlineStr">
-        <is>
-          <t>≥8%</t>
-        </is>
-      </c>
-      <c r="D6" s="35" t="inlineStr">
-        <is>
-          <t>5-8% regular / &lt;5% mejorar</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="36" t="inlineStr">
-        <is>
-          <t>ONE Multimedia</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>≥5</t>
-        </is>
-      </c>
-      <c r="C7" s="34" t="inlineStr">
-        <is>
-          <t>≥5</t>
-        </is>
-      </c>
-      <c r="D7" s="35" t="inlineStr">
-        <is>
-          <t>3-5 regular / &lt;3 mejorar</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/informes/informe_seguimiento_fernando_industriales.xlsx
+++ b/informes/informe_seguimiento_fernando_industriales.xlsx
@@ -2342,7 +2342,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Fecha: 06/05/2026</t>
+          <t>Fecha: 07/05/2026</t>
         </is>
       </c>
     </row>
@@ -2549,6 +2549,11 @@
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Observaciones</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>Grado de cumplimentación</t>
         </is>
@@ -2563,6 +2568,7 @@
       <c r="B37" s="9" t="inlineStr"/>
       <c r="C37" s="9" t="inlineStr"/>
       <c r="D37" s="9" t="inlineStr"/>
+      <c r="E37" s="9" t="inlineStr"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="13" t="inlineStr">
@@ -2573,6 +2579,7 @@
       <c r="B38" s="13" t="inlineStr"/>
       <c r="C38" s="13" t="inlineStr"/>
       <c r="D38" s="13" t="inlineStr"/>
+      <c r="E38" s="13" t="inlineStr"/>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="9" t="inlineStr">
@@ -2583,6 +2590,7 @@
       <c r="B39" s="9" t="inlineStr"/>
       <c r="C39" s="9" t="inlineStr"/>
       <c r="D39" s="9" t="inlineStr"/>
+      <c r="E39" s="9" t="inlineStr"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="13" t="inlineStr">
@@ -2593,6 +2601,7 @@
       <c r="B40" s="13" t="inlineStr"/>
       <c r="C40" s="13" t="inlineStr"/>
       <c r="D40" s="13" t="inlineStr"/>
+      <c r="E40" s="13" t="inlineStr"/>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
@@ -2603,6 +2612,7 @@
       <c r="B41" s="9" t="inlineStr"/>
       <c r="C41" s="9" t="inlineStr"/>
       <c r="D41" s="9" t="inlineStr"/>
+      <c r="E41" s="9" t="inlineStr"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="13" t="inlineStr">
@@ -2613,6 +2623,7 @@
       <c r="B42" s="13" t="inlineStr"/>
       <c r="C42" s="13" t="inlineStr"/>
       <c r="D42" s="13" t="inlineStr"/>
+      <c r="E42" s="13" t="inlineStr"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="9" t="inlineStr">
@@ -2623,6 +2634,7 @@
       <c r="B43" s="9" t="inlineStr"/>
       <c r="C43" s="9" t="inlineStr"/>
       <c r="D43" s="9" t="inlineStr"/>
+      <c r="E43" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="26">
@@ -3018,7 +3030,7 @@
       </c>
       <c r="D29" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>&lt;20</t>
         </is>
       </c>
     </row>

--- a/informes/informe_seguimiento_fernando_industriales.xlsx
+++ b/informes/informe_seguimiento_fernando_industriales.xlsx
@@ -2314,7 +2314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2438,78 +2438,78 @@
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>Sin datos registrados</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>PUNTOS POSITIVOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>Servicios Rápidos (en el día): 65,85% — 2/2 pts  |  Referencia: 0pts &lt;40% | 1pt ≥40% | 2pts ≥45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>PUNTOS A MEJORAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>Satisfacción General (CEM): 4,47 — 0/2 pts  |  Referencia: 0pts &lt;4,52 | 1pt ≥4,52 | 2pts ≥4,62</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>Medidas de Servicio (EC28): 9,52% — 0/2 pts  |  Referencia: 0pts &gt;5% | 1pt ≤5% | 2pts ≤3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>Conectividad Posventa: 17,48% — 1/2 pts  |  Referencia: 0pts &lt;10% | 1pt ≥10% | 2pts ≥25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>8. ONE KVPS</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>PUNTOS POSITIVOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>Instalación ONE: Rivas VW / Industriales (30070)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="inlineStr">
-        <is>
-          <t>Multimedia Acum.: 6,6 (media equipo: 6,2; bueno ≥5) — en rango positivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="14" t="inlineStr">
-        <is>
-          <t>PUNTOS A MEJORAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>Score SEM: 6,1 (media equipo: 7,3) — por debajo de la media</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B32" s="20" t="inlineStr">
-        <is>
-          <t>Service CAM Acum.: 7% (media equipo: 8%; bueno ≥8%) — en rango regular</t>
         </is>
       </c>
     </row>
@@ -2521,149 +2521,209 @@
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
+          <t>Instalación ONE: Rivas VW / Industriales (30070)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>Multimedia Acum.: 6,6 (media equipo: 6,2; bueno ≥5) — en rango positivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>PUNTOS A MEJORAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>Score SEM: 6,1 (media equipo: 7,3) — por debajo de la media</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>Service CAM Acum.: 7% (media equipo: 8%; bueno ≥8%) — en rango regular</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="inlineStr">
+        <is>
           <t>Diferidos Acum.: 3% (media equipo: 16%; bueno ≥8%) — por debajo del objetivo</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>9. Tareas pendientes</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>Fecha límite</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>Grado de cumplimentación</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>Utilizar el Laser de desgaste</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr"/>
-      <c r="C37" s="9" t="inlineStr"/>
-      <c r="D37" s="9" t="inlineStr"/>
-      <c r="E37" s="9" t="inlineStr"/>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr"/>
+      <c r="C42" s="9" t="inlineStr"/>
+      <c r="D42" s="9" t="inlineStr"/>
+      <c r="E42" s="9" t="inlineStr"/>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="13" t="inlineStr">
         <is>
           <t>Radar y desgaste</t>
         </is>
       </c>
-      <c r="B38" s="13" t="inlineStr"/>
-      <c r="C38" s="13" t="inlineStr"/>
-      <c r="D38" s="13" t="inlineStr"/>
-      <c r="E38" s="13" t="inlineStr"/>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="B43" s="13" t="inlineStr"/>
+      <c r="C43" s="13" t="inlineStr"/>
+      <c r="D43" s="13" t="inlineStr"/>
+      <c r="E43" s="13" t="inlineStr"/>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>Deferencias y demás</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr"/>
-      <c r="C39" s="9" t="inlineStr"/>
-      <c r="D39" s="9" t="inlineStr"/>
-      <c r="E39" s="9" t="inlineStr"/>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr"/>
+      <c r="C44" s="9" t="inlineStr"/>
+      <c r="D44" s="9" t="inlineStr"/>
+      <c r="E44" s="9" t="inlineStr"/>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="13" t="inlineStr">
         <is>
           <t>One Score</t>
         </is>
       </c>
-      <c r="B40" s="13" t="inlineStr"/>
-      <c r="C40" s="13" t="inlineStr"/>
-      <c r="D40" s="13" t="inlineStr"/>
-      <c r="E40" s="13" t="inlineStr"/>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="B45" s="13" t="inlineStr"/>
+      <c r="C45" s="13" t="inlineStr"/>
+      <c r="D45" s="13" t="inlineStr"/>
+      <c r="E45" s="13" t="inlineStr"/>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>Servicio de Movilidad</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr"/>
-      <c r="C41" s="9" t="inlineStr"/>
-      <c r="D41" s="9" t="inlineStr"/>
-      <c r="E41" s="9" t="inlineStr"/>
-    </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="13" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr"/>
+      <c r="C46" s="9" t="inlineStr"/>
+      <c r="D46" s="9" t="inlineStr"/>
+      <c r="E46" s="9" t="inlineStr"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="13" t="inlineStr">
         <is>
           <t>Mantenimiento &lt;24h</t>
         </is>
       </c>
-      <c r="B42" s="13" t="inlineStr"/>
-      <c r="C42" s="13" t="inlineStr"/>
-      <c r="D42" s="13" t="inlineStr"/>
-      <c r="E42" s="13" t="inlineStr"/>
-    </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="B47" s="13" t="inlineStr"/>
+      <c r="C47" s="13" t="inlineStr"/>
+      <c r="D47" s="13" t="inlineStr"/>
+      <c r="E47" s="13" t="inlineStr"/>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>Diferidos</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr"/>
-      <c r="C43" s="9" t="inlineStr"/>
-      <c r="D43" s="9" t="inlineStr"/>
-      <c r="E43" s="9" t="inlineStr"/>
+      <c r="B48" s="9" t="inlineStr"/>
+      <c r="C48" s="9" t="inlineStr"/>
+      <c r="D48" s="9" t="inlineStr"/>
+      <c r="E48" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="B31:F31"/>
+  <mergeCells count="31">
+    <mergeCell ref="B25:F25"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A21:F21"/>
+    <mergeCell ref="B27:F27"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A32:F32"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A35:F35"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B34:F34"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="A40:F40"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3072,10 +3132,8 @@
       <c r="B33" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="C33" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C33" s="29" t="n">
+        <v>3</v>
       </c>
       <c r="D33" s="28" t="inlineStr">
         <is>
